--- a/data/2_bundesliga_prediction_matchday_27_2025.xlsx
+++ b/data/2_bundesliga_prediction_matchday_27_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meinert\Documents\fussballanalyse\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tobiasmeinert/Documents/GitHub/fussballanalyse/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94730E7A-A37D-482D-8127-FA874AF94A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -223,8 +223,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -238,6 +238,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -288,12 +289,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -594,15 +595,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -660,7 +661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -689,7 +690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -718,7 +719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -747,7 +748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -776,7 +777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -805,7 +806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -834,7 +835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -863,7 +864,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -892,7 +893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -921,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -950,7 +951,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -979,7 +980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1008,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1037,7 +1038,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1066,7 +1067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1095,7 +1096,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1124,7 +1125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1161,12 +1162,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1225,7 +1226,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1284,7 +1285,7 @@
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1343,7 +1344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1402,7 +1403,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1461,7 +1462,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1520,7 +1521,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1579,7 +1580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1638,7 +1639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1697,7 +1698,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1756,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1815,7 +1816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1874,7 +1875,7 @@
         <v>0.41199999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1933,7 +1934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1992,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -2051,7 +2052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -2110,7 +2111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -2169,7 +2170,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -2228,7 +2229,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2295,12 +2296,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C359"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2311,7 +2312,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -2322,7 +2323,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2333,7 +2334,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2344,7 +2345,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2355,7 +2356,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2366,7 +2367,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2377,7 +2378,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2399,7 +2400,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2410,7 +2411,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2421,7 +2422,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -2443,7 +2444,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2454,7 +2455,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -2465,7 +2466,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -2476,7 +2477,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2487,7 +2488,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2498,7 +2499,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -2509,7 +2510,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2520,7 +2521,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2531,7 +2532,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -2542,7 +2543,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -2553,7 +2554,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -2564,7 +2565,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -2575,7 +2576,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -2586,7 +2587,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -2597,7 +2598,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -2608,7 +2609,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -2619,7 +2620,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -2630,7 +2631,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -2641,7 +2642,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -2652,7 +2653,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -2663,7 +2664,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -2674,7 +2675,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -2685,7 +2686,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -2696,7 +2697,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -2718,7 +2719,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -2729,7 +2730,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -2740,7 +2741,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -2751,7 +2752,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -2762,7 +2763,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -2773,7 +2774,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -2784,7 +2785,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -2795,7 +2796,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -2806,7 +2807,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -2817,7 +2818,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -2828,7 +2829,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>22</v>
       </c>
@@ -2839,7 +2840,7 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>22</v>
       </c>
@@ -2850,7 +2851,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>22</v>
       </c>
@@ -2861,7 +2862,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>22</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -2883,7 +2884,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -2894,7 +2895,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -2905,7 +2906,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -2916,7 +2917,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -2927,7 +2928,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -2938,7 +2939,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>22</v>
       </c>
@@ -2949,7 +2950,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>22</v>
       </c>
@@ -2960,7 +2961,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>22</v>
       </c>
@@ -2971,7 +2972,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>19</v>
       </c>
@@ -2982,7 +2983,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>19</v>
       </c>
@@ -2993,7 +2994,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>19</v>
       </c>
@@ -3004,7 +3005,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -3015,7 +3016,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -3026,7 +3027,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -3037,7 +3038,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>19</v>
       </c>
@@ -3048,7 +3049,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -3059,7 +3060,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -3070,7 +3071,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>19</v>
       </c>
@@ -3081,7 +3082,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>19</v>
       </c>
@@ -3092,7 +3093,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -3103,7 +3104,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>19</v>
       </c>
@@ -3114,7 +3115,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>19</v>
       </c>
@@ -3125,7 +3126,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -3136,7 +3137,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>19</v>
       </c>
@@ -3147,7 +3148,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -3158,7 +3159,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>19</v>
       </c>
@@ -3169,7 +3170,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>19</v>
       </c>
@@ -3180,7 +3181,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>19</v>
       </c>
@@ -3191,7 +3192,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>20</v>
       </c>
@@ -3202,7 +3203,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -3213,7 +3214,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>20</v>
       </c>
@@ -3224,7 +3225,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>20</v>
       </c>
@@ -3235,7 +3236,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>20</v>
       </c>
@@ -3246,7 +3247,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>20</v>
       </c>
@@ -3257,7 +3258,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>20</v>
       </c>
@@ -3268,7 +3269,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>20</v>
       </c>
@@ -3279,7 +3280,7 @@
         <v>0.13200000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>20</v>
       </c>
@@ -3290,7 +3291,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>20</v>
       </c>
@@ -3301,7 +3302,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>20</v>
       </c>
@@ -3312,7 +3313,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>20</v>
       </c>
@@ -3323,7 +3324,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>20</v>
       </c>
@@ -3334,7 +3335,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>20</v>
       </c>
@@ -3345,7 +3346,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>20</v>
       </c>
@@ -3356,7 +3357,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>20</v>
       </c>
@@ -3367,7 +3368,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>20</v>
       </c>
@@ -3378,7 +3379,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>20</v>
       </c>
@@ -3389,7 +3390,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>20</v>
       </c>
@@ -3400,7 +3401,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>20</v>
       </c>
@@ -3411,7 +3412,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>20</v>
       </c>
@@ -3422,7 +3423,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>13</v>
       </c>
@@ -3433,7 +3434,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>13</v>
       </c>
@@ -3444,7 +3445,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>13</v>
       </c>
@@ -3455,7 +3456,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>13</v>
       </c>
@@ -3466,7 +3467,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>13</v>
       </c>
@@ -3477,7 +3478,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>13</v>
       </c>
@@ -3488,7 +3489,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>13</v>
       </c>
@@ -3499,7 +3500,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -3510,7 +3511,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>13</v>
       </c>
@@ -3521,7 +3522,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>13</v>
       </c>
@@ -3532,7 +3533,7 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>13</v>
       </c>
@@ -3543,7 +3544,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>13</v>
       </c>
@@ -3554,7 +3555,7 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>13</v>
       </c>
@@ -3565,7 +3566,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>13</v>
       </c>
@@ -3576,7 +3577,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>13</v>
       </c>
@@ -3587,7 +3588,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>13</v>
       </c>
@@ -3598,7 +3599,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -3609,7 +3610,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>13</v>
       </c>
@@ -3620,7 +3621,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>13</v>
       </c>
@@ -3631,7 +3632,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>13</v>
       </c>
@@ -3642,7 +3643,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -3653,7 +3654,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>14</v>
       </c>
@@ -3664,7 +3665,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>14</v>
       </c>
@@ -3675,7 +3676,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>14</v>
       </c>
@@ -3686,7 +3687,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>14</v>
       </c>
@@ -3697,7 +3698,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>14</v>
       </c>
@@ -3708,7 +3709,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>14</v>
       </c>
@@ -3719,7 +3720,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>14</v>
       </c>
@@ -3730,7 +3731,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>14</v>
       </c>
@@ -3741,7 +3742,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>14</v>
       </c>
@@ -3752,7 +3753,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>14</v>
       </c>
@@ -3763,7 +3764,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>14</v>
       </c>
@@ -3774,7 +3775,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>14</v>
       </c>
@@ -3785,7 +3786,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>14</v>
       </c>
@@ -3796,7 +3797,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>14</v>
       </c>
@@ -3807,7 +3808,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>14</v>
       </c>
@@ -3818,7 +3819,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>14</v>
       </c>
@@ -3829,7 +3830,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>14</v>
       </c>
@@ -3840,7 +3841,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>14</v>
       </c>
@@ -3851,7 +3852,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>21</v>
       </c>
@@ -3862,7 +3863,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>21</v>
       </c>
@@ -3873,7 +3874,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>21</v>
       </c>
@@ -3884,7 +3885,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>21</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>21</v>
       </c>
@@ -3906,7 +3907,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>21</v>
       </c>
@@ -3917,7 +3918,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>21</v>
       </c>
@@ -3928,7 +3929,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>21</v>
       </c>
@@ -3939,7 +3940,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>21</v>
       </c>
@@ -3950,7 +3951,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>21</v>
       </c>
@@ -3961,7 +3962,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>21</v>
       </c>
@@ -3972,7 +3973,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>21</v>
       </c>
@@ -3983,7 +3984,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>21</v>
       </c>
@@ -3994,7 +3995,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>21</v>
       </c>
@@ -4005,7 +4006,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>21</v>
       </c>
@@ -4016,7 +4017,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>21</v>
       </c>
@@ -4027,7 +4028,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>21</v>
       </c>
@@ -4038,7 +4039,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>21</v>
       </c>
@@ -4049,7 +4050,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>21</v>
       </c>
@@ -4060,7 +4061,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>21</v>
       </c>
@@ -4071,7 +4072,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>21</v>
       </c>
@@ -4082,7 +4083,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>15</v>
       </c>
@@ -4093,7 +4094,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>15</v>
       </c>
@@ -4104,7 +4105,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>15</v>
       </c>
@@ -4115,7 +4116,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>15</v>
       </c>
@@ -4126,7 +4127,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>15</v>
       </c>
@@ -4137,7 +4138,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>15</v>
       </c>
@@ -4148,7 +4149,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>15</v>
       </c>
@@ -4159,7 +4160,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>15</v>
       </c>
@@ -4170,7 +4171,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>15</v>
       </c>
@@ -4181,7 +4182,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>15</v>
       </c>
@@ -4192,7 +4193,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -4203,7 +4204,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>15</v>
       </c>
@@ -4214,7 +4215,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>15</v>
       </c>
@@ -4225,7 +4226,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>15</v>
       </c>
@@ -4236,7 +4237,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>15</v>
       </c>
@@ -4247,7 +4248,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>15</v>
       </c>
@@ -4258,7 +4259,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>15</v>
       </c>
@@ -4269,7 +4270,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>15</v>
       </c>
@@ -4280,7 +4281,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>15</v>
       </c>
@@ -4291,7 +4292,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>15</v>
       </c>
@@ -4302,7 +4303,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>17</v>
       </c>
@@ -4313,7 +4314,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>17</v>
       </c>
@@ -4324,7 +4325,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>17</v>
       </c>
@@ -4335,7 +4336,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>17</v>
       </c>
@@ -4346,7 +4347,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>17</v>
       </c>
@@ -4357,7 +4358,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>17</v>
       </c>
@@ -4368,7 +4369,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>17</v>
       </c>
@@ -4379,7 +4380,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>17</v>
       </c>
@@ -4390,7 +4391,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>17</v>
       </c>
@@ -4401,7 +4402,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>17</v>
       </c>
@@ -4412,7 +4413,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>17</v>
       </c>
@@ -4423,7 +4424,7 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -4434,7 +4435,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -4445,7 +4446,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>17</v>
       </c>
@@ -4456,7 +4457,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>17</v>
       </c>
@@ -4467,7 +4468,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>17</v>
       </c>
@@ -4478,7 +4479,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>17</v>
       </c>
@@ -4489,7 +4490,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>17</v>
       </c>
@@ -4500,7 +4501,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>17</v>
       </c>
@@ -4511,7 +4512,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>17</v>
       </c>
@@ -4522,7 +4523,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>26</v>
       </c>
@@ -4533,7 +4534,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>26</v>
       </c>
@@ -4544,7 +4545,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>26</v>
       </c>
@@ -4555,7 +4556,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>26</v>
       </c>
@@ -4566,7 +4567,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>26</v>
       </c>
@@ -4577,7 +4578,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>26</v>
       </c>
@@ -4588,7 +4589,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>26</v>
       </c>
@@ -4599,7 +4600,7 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>26</v>
       </c>
@@ -4610,7 +4611,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>26</v>
       </c>
@@ -4621,7 +4622,7 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>26</v>
       </c>
@@ -4632,7 +4633,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>26</v>
       </c>
@@ -4643,7 +4644,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>26</v>
       </c>
@@ -4654,7 +4655,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>26</v>
       </c>
@@ -4665,7 +4666,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>26</v>
       </c>
@@ -4676,7 +4677,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>26</v>
       </c>
@@ -4687,7 +4688,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>26</v>
       </c>
@@ -4698,7 +4699,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>26</v>
       </c>
@@ -4709,7 +4710,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>26</v>
       </c>
@@ -4720,7 +4721,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>11</v>
       </c>
@@ -4731,7 +4732,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>11</v>
       </c>
@@ -4742,7 +4743,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>11</v>
       </c>
@@ -4753,7 +4754,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>11</v>
       </c>
@@ -4764,7 +4765,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>11</v>
       </c>
@@ -4775,7 +4776,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>11</v>
       </c>
@@ -4786,7 +4787,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>11</v>
       </c>
@@ -4797,7 +4798,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>11</v>
       </c>
@@ -4808,7 +4809,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>11</v>
       </c>
@@ -4819,7 +4820,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>11</v>
       </c>
@@ -4830,7 +4831,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>11</v>
       </c>
@@ -4841,7 +4842,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>11</v>
       </c>
@@ -4852,7 +4853,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>11</v>
       </c>
@@ -4863,7 +4864,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>11</v>
       </c>
@@ -4874,7 +4875,7 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>11</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>11</v>
       </c>
@@ -4896,7 +4897,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>11</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>11</v>
       </c>
@@ -4918,7 +4919,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>11</v>
       </c>
@@ -4929,7 +4930,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>11</v>
       </c>
@@ -4940,7 +4941,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>11</v>
       </c>
@@ -4951,7 +4952,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>10</v>
       </c>
@@ -4962,7 +4963,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>10</v>
       </c>
@@ -4973,7 +4974,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>10</v>
       </c>
@@ -4984,7 +4985,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>10</v>
       </c>
@@ -4995,7 +4996,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>10</v>
       </c>
@@ -5006,7 +5007,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>10</v>
       </c>
@@ -5017,7 +5018,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>10</v>
       </c>
@@ -5028,7 +5029,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -5039,7 +5040,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>10</v>
       </c>
@@ -5050,7 +5051,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>10</v>
       </c>
@@ -5061,7 +5062,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>10</v>
       </c>
@@ -5072,7 +5073,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>10</v>
       </c>
@@ -5083,7 +5084,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>10</v>
       </c>
@@ -5094,7 +5095,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>10</v>
       </c>
@@ -5105,7 +5106,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>10</v>
       </c>
@@ -5116,7 +5117,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>10</v>
       </c>
@@ -5127,7 +5128,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>10</v>
       </c>
@@ -5138,7 +5139,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>10</v>
       </c>
@@ -5149,7 +5150,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>10</v>
       </c>
@@ -5160,7 +5161,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>10</v>
       </c>
@@ -5171,7 +5172,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>12</v>
       </c>
@@ -5182,7 +5183,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>12</v>
       </c>
@@ -5193,7 +5194,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>12</v>
       </c>
@@ -5204,7 +5205,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>12</v>
       </c>
@@ -5215,7 +5216,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>12</v>
       </c>
@@ -5226,7 +5227,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>12</v>
       </c>
@@ -5237,7 +5238,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>12</v>
       </c>
@@ -5248,7 +5249,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>12</v>
       </c>
@@ -5259,7 +5260,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>12</v>
       </c>
@@ -5270,7 +5271,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>12</v>
       </c>
@@ -5281,7 +5282,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>12</v>
       </c>
@@ -5292,7 +5293,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>12</v>
       </c>
@@ -5303,7 +5304,7 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>12</v>
       </c>
@@ -5314,7 +5315,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>12</v>
       </c>
@@ -5325,7 +5326,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>12</v>
       </c>
@@ -5336,7 +5337,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>12</v>
       </c>
@@ -5347,7 +5348,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>12</v>
       </c>
@@ -5358,7 +5359,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>12</v>
       </c>
@@ -5369,7 +5370,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>12</v>
       </c>
@@ -5380,7 +5381,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>12</v>
       </c>
@@ -5391,7 +5392,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>12</v>
       </c>
@@ -5402,7 +5403,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>9</v>
       </c>
@@ -5413,7 +5414,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>9</v>
       </c>
@@ -5424,7 +5425,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>9</v>
       </c>
@@ -5435,7 +5436,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>9</v>
       </c>
@@ -5446,7 +5447,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>9</v>
       </c>
@@ -5457,7 +5458,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>9</v>
       </c>
@@ -5468,7 +5469,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>9</v>
       </c>
@@ -5479,7 +5480,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>9</v>
       </c>
@@ -5490,7 +5491,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>9</v>
       </c>
@@ -5501,7 +5502,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>9</v>
       </c>
@@ -5512,7 +5513,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>9</v>
       </c>
@@ -5523,7 +5524,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>9</v>
       </c>
@@ -5534,7 +5535,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>9</v>
       </c>
@@ -5545,7 +5546,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>9</v>
       </c>
@@ -5556,7 +5557,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>9</v>
       </c>
@@ -5567,7 +5568,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>9</v>
       </c>
@@ -5578,7 +5579,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>9</v>
       </c>
@@ -5589,7 +5590,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>9</v>
       </c>
@@ -5600,7 +5601,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>9</v>
       </c>
@@ -5611,7 +5612,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>23</v>
       </c>
@@ -5622,7 +5623,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>23</v>
       </c>
@@ -5633,7 +5634,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>23</v>
       </c>
@@ -5644,7 +5645,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>23</v>
       </c>
@@ -5655,7 +5656,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>23</v>
       </c>
@@ -5666,7 +5667,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>23</v>
       </c>
@@ -5677,7 +5678,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>23</v>
       </c>
@@ -5688,7 +5689,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>23</v>
       </c>
@@ -5699,7 +5700,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>23</v>
       </c>
@@ -5710,7 +5711,7 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>23</v>
       </c>
@@ -5721,7 +5722,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>23</v>
       </c>
@@ -5732,7 +5733,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>23</v>
       </c>
@@ -5743,7 +5744,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>23</v>
       </c>
@@ -5754,7 +5755,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>23</v>
       </c>
@@ -5765,7 +5766,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>23</v>
       </c>
@@ -5776,7 +5777,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>23</v>
       </c>
@@ -5787,7 +5788,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>23</v>
       </c>
@@ -5798,7 +5799,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>23</v>
       </c>
@@ -5809,7 +5810,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>23</v>
       </c>
@@ -5820,7 +5821,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>23</v>
       </c>
@@ -5831,7 +5832,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>24</v>
       </c>
@@ -5842,7 +5843,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>24</v>
       </c>
@@ -5853,7 +5854,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>24</v>
       </c>
@@ -5864,7 +5865,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>24</v>
       </c>
@@ -5875,7 +5876,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>24</v>
       </c>
@@ -5886,7 +5887,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>24</v>
       </c>
@@ -5897,7 +5898,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>24</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>24</v>
       </c>
@@ -5919,7 +5920,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>24</v>
       </c>
@@ -5930,7 +5931,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>24</v>
       </c>
@@ -5941,7 +5942,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>24</v>
       </c>
@@ -5952,7 +5953,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>24</v>
       </c>
@@ -5963,7 +5964,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>24</v>
       </c>
@@ -5974,7 +5975,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>24</v>
       </c>
@@ -5985,7 +5986,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>24</v>
       </c>
@@ -5996,7 +5997,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>24</v>
       </c>
@@ -6007,7 +6008,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>24</v>
       </c>
@@ -6018,7 +6019,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>18</v>
       </c>
@@ -6029,7 +6030,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>18</v>
       </c>
@@ -6040,7 +6041,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>18</v>
       </c>
@@ -6051,7 +6052,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>18</v>
       </c>
@@ -6062,7 +6063,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>18</v>
       </c>
@@ -6073,7 +6074,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>18</v>
       </c>
@@ -6084,7 +6085,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>18</v>
       </c>
@@ -6095,7 +6096,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>18</v>
       </c>
@@ -6106,7 +6107,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>18</v>
       </c>
@@ -6117,7 +6118,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>18</v>
       </c>
@@ -6128,7 +6129,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>18</v>
       </c>
@@ -6139,7 +6140,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>18</v>
       </c>
@@ -6150,7 +6151,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>18</v>
       </c>
@@ -6161,7 +6162,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>18</v>
       </c>
@@ -6172,7 +6173,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>18</v>
       </c>
@@ -6183,7 +6184,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>18</v>
       </c>
@@ -6194,7 +6195,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>18</v>
       </c>
@@ -6205,7 +6206,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>18</v>
       </c>
@@ -6216,7 +6217,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>18</v>
       </c>
@@ -6227,7 +6228,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>18</v>
       </c>
@@ -6238,7 +6239,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>18</v>
       </c>
@@ -6257,9 +6258,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C183"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6270,7 +6271,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -6281,7 +6282,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -6292,7 +6293,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -6303,7 +6304,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -6314,7 +6315,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -6325,7 +6326,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -6336,7 +6337,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -6347,7 +6348,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -6358,7 +6359,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -6369,7 +6370,7 @@
         <v>0.161</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -6380,7 +6381,7 @@
         <v>0.19900000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -6391,7 +6392,7 @@
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -6402,7 +6403,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -6413,7 +6414,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -6424,7 +6425,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -6435,7 +6436,7 @@
         <v>0.32300000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -6446,7 +6447,7 @@
         <v>0.24199999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -6457,7 +6458,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -6468,7 +6469,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -6479,7 +6480,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -6490,7 +6491,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -6501,7 +6502,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -6512,7 +6513,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -6523,7 +6524,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -6534,7 +6535,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -6545,7 +6546,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -6556,7 +6557,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -6567,7 +6568,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -6578,7 +6579,7 @@
         <v>0.127</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -6589,7 +6590,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -6600,7 +6601,7 @@
         <v>0.13100000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -6611,7 +6612,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -6622,7 +6623,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>22</v>
       </c>
@@ -6633,7 +6634,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -6644,7 +6645,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -6655,7 +6656,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -6666,7 +6667,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -6677,7 +6678,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -6688,7 +6689,7 @@
         <v>0.129</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -6699,7 +6700,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -6710,7 +6711,7 @@
         <v>0.14599999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -6721,7 +6722,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -6732,7 +6733,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -6743,7 +6744,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -6754,7 +6755,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -6765,7 +6766,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -6776,7 +6777,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>20</v>
       </c>
@@ -6787,7 +6788,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -6798,7 +6799,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>20</v>
       </c>
@@ -6809,7 +6810,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>20</v>
       </c>
@@ -6820,7 +6821,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -6831,7 +6832,7 @@
         <v>0.14599999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>20</v>
       </c>
@@ -6842,7 +6843,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -6853,7 +6854,7 @@
         <v>0.14599999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>20</v>
       </c>
@@ -6864,7 +6865,7 @@
         <v>0.13100000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -6875,7 +6876,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>20</v>
       </c>
@@ -6886,7 +6887,7 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -6897,7 +6898,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -6908,7 +6909,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -6919,7 +6920,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -6930,7 +6931,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -6941,7 +6942,7 @@
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -6952,7 +6953,7 @@
         <v>0.19400000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -6963,7 +6964,7 @@
         <v>0.253</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -6974,7 +6975,7 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -6985,7 +6986,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -6996,7 +6997,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>13</v>
       </c>
@@ -7007,7 +7008,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -7018,7 +7019,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -7029,7 +7030,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -7040,7 +7041,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -7051,7 +7052,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -7062,7 +7063,7 @@
         <v>0.23499999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -7073,7 +7074,7 @@
         <v>0.41199999999999998</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -7084,7 +7085,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -7095,7 +7096,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -7106,7 +7107,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>21</v>
       </c>
@@ -7117,7 +7118,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>21</v>
       </c>
@@ -7128,7 +7129,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>21</v>
       </c>
@@ -7139,7 +7140,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -7150,7 +7151,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>21</v>
       </c>
@@ -7161,7 +7162,7 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>21</v>
       </c>
@@ -7172,7 +7173,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>21</v>
       </c>
@@ -7183,7 +7184,7 @@
         <v>0.13100000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>21</v>
       </c>
@@ -7194,7 +7195,7 @@
         <v>0.14099999999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>21</v>
       </c>
@@ -7205,7 +7206,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>21</v>
       </c>
@@ -7216,7 +7217,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>21</v>
       </c>
@@ -7227,7 +7228,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>21</v>
       </c>
@@ -7238,7 +7239,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -7249,7 +7250,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -7260,7 +7261,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -7271,7 +7272,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -7282,7 +7283,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -7293,7 +7294,7 @@
         <v>0.57799999999999996</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>15</v>
       </c>
@@ -7304,7 +7305,7 @@
         <v>0.18099999999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>15</v>
       </c>
@@ -7315,7 +7316,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>15</v>
       </c>
@@ -7326,7 +7327,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>15</v>
       </c>
@@ -7337,7 +7338,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>15</v>
       </c>
@@ -7348,7 +7349,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>15</v>
       </c>
@@ -7359,7 +7360,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -7370,7 +7371,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -7381,7 +7382,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -7392,7 +7393,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>17</v>
       </c>
@@ -7403,7 +7404,7 @@
         <v>0.23499999999999999</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>17</v>
       </c>
@@ -7414,7 +7415,7 @@
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -7425,7 +7426,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -7436,7 +7437,7 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -7447,7 +7448,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -7458,7 +7459,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -7469,7 +7470,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -7480,7 +7481,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>26</v>
       </c>
@@ -7491,7 +7492,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>26</v>
       </c>
@@ -7502,7 +7503,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>26</v>
       </c>
@@ -7513,7 +7514,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>26</v>
       </c>
@@ -7524,7 +7525,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>26</v>
       </c>
@@ -7535,7 +7536,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>26</v>
       </c>
@@ -7546,7 +7547,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>26</v>
       </c>
@@ -7557,7 +7558,7 @@
         <v>0.13200000000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>26</v>
       </c>
@@ -7568,7 +7569,7 @@
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>26</v>
       </c>
@@ -7579,7 +7580,7 @@
         <v>0.41199999999999998</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -7590,7 +7591,7 @@
         <v>0.161</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -7601,7 +7602,7 @@
         <v>0.20200000000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -7612,7 +7613,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -7623,7 +7624,7 @@
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -7634,7 +7635,7 @@
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -7645,7 +7646,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -7656,7 +7657,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -7667,7 +7668,7 @@
         <v>0.27800000000000002</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -7678,7 +7679,7 @@
         <v>0.246</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -7689,7 +7690,7 @@
         <v>0.19400000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -7700,7 +7701,7 @@
         <v>0.14599999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>10</v>
       </c>
@@ -7711,7 +7712,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>10</v>
       </c>
@@ -7722,7 +7723,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -7733,7 +7734,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>12</v>
       </c>
@@ -7744,7 +7745,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>12</v>
       </c>
@@ -7755,7 +7756,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>12</v>
       </c>
@@ -7766,7 +7767,7 @@
         <v>0.222</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>12</v>
       </c>
@@ -7777,7 +7778,7 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>12</v>
       </c>
@@ -7788,7 +7789,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>12</v>
       </c>
@@ -7799,7 +7800,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>12</v>
       </c>
@@ -7810,7 +7811,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>9</v>
       </c>
@@ -7821,7 +7822,7 @@
         <v>0.34799999999999998</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>9</v>
       </c>
@@ -7832,7 +7833,7 @@
         <v>0.246</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -7843,7 +7844,7 @@
         <v>0.17599999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>9</v>
       </c>
@@ -7854,7 +7855,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>9</v>
       </c>
@@ -7865,7 +7866,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>9</v>
       </c>
@@ -7876,7 +7877,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>9</v>
       </c>
@@ -7887,7 +7888,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>23</v>
       </c>
@@ -7898,7 +7899,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>23</v>
       </c>
@@ -7909,7 +7910,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>23</v>
       </c>
@@ -7920,7 +7921,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>23</v>
       </c>
@@ -7931,7 +7932,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>23</v>
       </c>
@@ -7942,7 +7943,7 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>23</v>
       </c>
@@ -7953,7 +7954,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>23</v>
       </c>
@@ -7964,7 +7965,7 @@
         <v>0.13700000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>23</v>
       </c>
@@ -7975,7 +7976,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>23</v>
       </c>
@@ -7986,7 +7987,7 @@
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>23</v>
       </c>
@@ -7997,7 +7998,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>23</v>
       </c>
@@ -8008,7 +8009,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>24</v>
       </c>
@@ -8019,7 +8020,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>24</v>
       </c>
@@ -8030,7 +8031,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>24</v>
       </c>
@@ -8041,7 +8042,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>24</v>
       </c>
@@ -8052,7 +8053,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>24</v>
       </c>
@@ -8063,7 +8064,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>24</v>
       </c>
@@ -8074,7 +8075,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>24</v>
       </c>
@@ -8085,7 +8086,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>24</v>
       </c>
@@ -8096,7 +8097,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>24</v>
       </c>
@@ -8107,7 +8108,7 @@
         <v>0.17100000000000001</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>24</v>
       </c>
@@ -8118,7 +8119,7 @@
         <v>0.18099999999999999</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>24</v>
       </c>
@@ -8129,7 +8130,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -8140,7 +8141,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -8151,7 +8152,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -8162,7 +8163,7 @@
         <v>0.159</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -8173,7 +8174,7 @@
         <v>0.214</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -8184,7 +8185,7 @@
         <v>0.20100000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -8195,7 +8196,7 @@
         <v>0.159</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -8206,7 +8207,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -8217,7 +8218,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -8228,7 +8229,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -8239,7 +8240,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -8250,7 +8251,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -8261,7 +8262,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -8280,19 +8281,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -8327,7 +8328,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>28</v>
       </c>
@@ -8362,7 +8363,7 @@
         <v>0.1202053430094798</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>28</v>
       </c>
@@ -8397,7 +8398,7 @@
         <v>0.1120353640913649</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>28</v>
       </c>
@@ -8432,7 +8433,7 @@
         <v>0.1230942831602886</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>28</v>
       </c>
@@ -8467,7 +8468,7 @@
         <v>8.1900492135268399E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>28</v>
       </c>
@@ -8502,7 +8503,7 @@
         <v>0.1158878483705761</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>28</v>
       </c>
@@ -8537,7 +8538,7 @@
         <v>0.1409480393728971</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>28</v>
       </c>
@@ -8572,7 +8573,7 @@
         <v>9.8679880451015722E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>28</v>
       </c>
@@ -8607,7 +8608,7 @@
         <v>9.8804642908485535E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>28</v>
       </c>
@@ -8642,7 +8643,7 @@
         <v>0.12629135576886169</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>29</v>
       </c>
@@ -8677,7 +8678,7 @@
         <v>0.1226944750697444</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>29</v>
       </c>
@@ -8712,7 +8713,7 @@
         <v>0.1015709301846496</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>29</v>
       </c>
@@ -8747,7 +8748,7 @@
         <v>0.10490566623098239</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>29</v>
       </c>
@@ -8782,7 +8783,7 @@
         <v>0.1285159343569941</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>29</v>
       </c>
@@ -8817,7 +8818,7 @@
         <v>9.1642812802235546E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>29</v>
       </c>
@@ -8852,7 +8853,7 @@
         <v>0.1085444050370773</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>29</v>
       </c>
@@ -8887,7 +8888,7 @@
         <v>8.9562980639981193E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>29</v>
       </c>
@@ -8922,7 +8923,7 @@
         <v>0.14432715970037971</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>29</v>
       </c>
@@ -8957,7 +8958,7 @@
         <v>0.1213065426432989</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>30</v>
       </c>
@@ -8992,7 +8993,7 @@
         <v>0.12644650442325711</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>30</v>
       </c>
@@ -9027,7 +9028,7 @@
         <v>9.9784231954366268E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>30</v>
       </c>
@@ -9062,7 +9063,7 @@
         <v>0.12961331784053229</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>30</v>
       </c>
@@ -9097,7 +9098,7 @@
         <v>0.11555597371336709</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>30</v>
       </c>
@@ -9132,7 +9133,7 @@
         <v>0.1112830992100407</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>30</v>
       </c>
@@ -9167,7 +9168,7 @@
         <v>0.12885161366347059</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>30</v>
       </c>
@@ -9202,7 +9203,7 @@
         <v>0.12515099172113001</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>30</v>
       </c>
@@ -9237,7 +9238,7 @@
         <v>8.8759239027993667E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>30</v>
       </c>
@@ -9272,7 +9273,7 @@
         <v>9.666050121862392E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>31</v>
       </c>
@@ -9307,7 +9308,7 @@
         <v>0.11110382243459491</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>31</v>
       </c>
@@ -9342,7 +9343,7 @@
         <v>0.1130384741046911</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>31</v>
       </c>
@@ -9377,7 +9378,7 @@
         <v>0.1284923227014369</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -9412,7 +9413,7 @@
         <v>0.1061627041558685</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
@@ -9447,7 +9448,7 @@
         <v>8.0278991404955743E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>31</v>
       </c>
@@ -9482,7 +9483,7 @@
         <v>0.13066700276084409</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>31</v>
       </c>
@@ -9517,7 +9518,7 @@
         <v>0.12737378216934339</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>31</v>
       </c>
@@ -9552,7 +9553,7 @@
         <v>0.1117550383491473</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>31</v>
       </c>
@@ -9587,7 +9588,7 @@
         <v>9.0696040102793557E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>32</v>
       </c>
@@ -9622,7 +9623,7 @@
         <v>8.882650072587113E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>32</v>
       </c>
@@ -9657,7 +9658,7 @@
         <v>0.1256352810833673</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>32</v>
       </c>
@@ -9692,7 +9693,7 @@
         <v>9.5327241662905488E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>32</v>
       </c>
@@ -9727,7 +9728,7 @@
         <v>0.1285772593022935</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>32</v>
       </c>
@@ -9762,7 +9763,7 @@
         <v>0.13745401541885191</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>32</v>
       </c>
@@ -9797,7 +9798,7 @@
         <v>8.1154879847648548E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>32</v>
       </c>
@@ -9832,7 +9833,7 @@
         <v>0.12987573759507071</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>32</v>
       </c>
@@ -9867,7 +9868,7 @@
         <v>0.1474619227480102</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>32</v>
       </c>
@@ -9902,7 +9903,7 @@
         <v>0.1025747103960853</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>33</v>
       </c>
@@ -9937,7 +9938,7 @@
         <v>0.13504197164951889</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>33</v>
       </c>
@@ -9972,7 +9973,7 @@
         <v>0.1040102808667389</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>33</v>
       </c>
@@ -10007,7 +10008,7 @@
         <v>0.1099086658889243</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>33</v>
       </c>
@@ -10042,7 +10043,7 @@
         <v>0.1231751075274061</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>33</v>
       </c>
@@ -10077,7 +10078,7 @@
         <v>0.1117548306820718</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>33</v>
       </c>
@@ -10112,7 +10113,7 @@
         <v>0.11175818097799239</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>33</v>
       </c>
@@ -10147,7 +10148,7 @@
         <v>9.0292964814989593E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>33</v>
       </c>
@@ -10182,7 +10183,7 @@
         <v>0.1112614588776788</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>33</v>
       </c>
@@ -10217,7 +10218,7 @@
         <v>0.10538806401578291</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>34</v>
       </c>
@@ -10252,7 +10253,7 @@
         <v>0.1124772312515262</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>34</v>
       </c>
@@ -10287,7 +10288,7 @@
         <v>9.4754319524741532E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>34</v>
       </c>
@@ -10322,7 +10323,7 @@
         <v>9.4111552471218995E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>34</v>
       </c>
@@ -10357,7 +10358,7 @@
         <v>0.118749827244478</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>34</v>
       </c>
@@ -10392,7 +10393,7 @@
         <v>0.10302047328588761</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>34</v>
       </c>
@@ -10427,7 +10428,7 @@
         <v>0.13137367975278649</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>34</v>
       </c>
@@ -10462,7 +10463,7 @@
         <v>0.13008287131764079</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>34</v>
       </c>
@@ -10497,7 +10498,7 @@
         <v>0.13074466492507891</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>34</v>
       </c>
